--- a/log/更新list.xlsx
+++ b/log/更新list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL PROJECT\log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL PROJECT - TEST_v4.2_20250509\log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079F5CA6-817F-4F84-87D9-2FB3FA97C4CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F6714E-9D06-4C88-8AA0-61C4E138E25E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,14 +392,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MP List Check Tool_v4.2_202505</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新list：
-1、	单独开一页或者放在Analyse页面，以代码方便维护为原则；
-2、	导入本地excel文件，统计【客诉记录】页面信息；
-3、	从IC型号、模组厂、玻璃厂、年度（以开始日期为准）、转接zAE与否、结案与否、客诉类型、负责人等多个维度筛选（支持任意组合）并生成直方图（X坐标为前面的维度，Y坐标为项目数量）；</t>
+    <t>MP List Check Tool_v4.2_20250509</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新list：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1、	Analyse页面，建立MP分析与客诉分析两个页面，将原Analyse页面内容移植到MP分析；
+2、	客诉分析页面：
+        a.从本地文件中读取excel文件的客诉记录sheet；
+        b.从IC型号、模组厂、玻璃厂、年度（以开始日期为准）、转接AE与否、结案与否、客诉类型、负责人等多个维度下拉框进行筛选（支持任意组合）并生成直方图（X坐标为前面的维度，Y坐标为项目数量）。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -407,7 +428,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,6 +498,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -522,13 +551,13 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -868,11 +897,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="69" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -898,33 +927,33 @@
       </c>
     </row>
     <row r="2" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+      <c r="A3" s="8"/>
     </row>
     <row r="4" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
     </row>
     <row r="5" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+      <c r="A5" s="8"/>
     </row>
     <row r="6" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
     </row>
     <row r="7" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="8"/>
     </row>
     <row r="8" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="8"/>
     </row>
     <row r="9" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
+      <c r="A9" s="8"/>
     </row>
     <row r="10" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
+      <c r="A10" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/log/更新list.xlsx
+++ b/log/更新list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL PROJECT - TEST_v4.2_20250509\log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP List Check Tool_v4.3_20250724\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F6714E-9D06-4C88-8AA0-61C4E138E25E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103AF526-83FB-4624-8BC6-0B36AB6D2C37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -396,6 +396,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>MP List Check Tool_v4.3_20250724</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -416,10 +420,50 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-1、	Analyse页面，建立MP分析与客诉分析两个页面，将原Analyse页面内容移植到MP分析；
-2、	客诉分析页面：
+1.Analyse页面，建立MP分析与客诉分析两个页面，将原Analyse页面内容移植到MP分析；
+2.客诉分析页面：
         a.从本地文件中读取excel文件的客诉记录sheet；
         b.从IC型号、模组厂、玻璃厂、年度（以开始日期为准）、转接AE与否、结案与否、客诉类型、负责人等多个维度下拉框进行筛选（支持任意组合）并生成直方图（X坐标为前面的维度，Y坐标为项目数量）。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新list：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.Check标签页:
+a.新增重复项目号检查，一键检查/分项检查均新增该功能，若有重复，则报fail并且打印重复位置；
+2.Analyse标签页：
+a.MP分析页面新增“等级”筛选选项，并且可按“等级”进行数据分析，目前支持V/A/G/-/NULL，其中NULL表示等级空白项目；
+b.MP分析/客诉分析中，IC型号、模组厂、玻璃厂、年度、等级、客诉类型、负责人均支持新增自定义关键字筛选，自定义规则如下：
+    i.方法1：在compare_information.xlsx表Sheet2中新增内容，重启TOOL即可；
+   ii.方法2：UI界面中，右键想要新增内容的下拉框，即进入编辑模式，输入需要新增的内容再右键保存即可（如右备注所示），其中ESC可退出编辑模式；
+  iii.自定义关键字中，玻璃厂与等级字符需要保持’大写字母‘，年度需要’年份+年度‘。
+3.bug修复
+a.修正Y轴刻度会出现小数点问题，保持刻度只出现整数；
+b.修正下拉框不是自定义时可编辑的bug.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -533,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -552,6 +596,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -574,6 +624,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>28805</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>516255</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9235</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1283970</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA2E0E5-B64D-41EB-99D5-D642D77FCD0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12906605" y="13203555"/>
+          <a:ext cx="2533130" cy="767715"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -840,24 +939,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
     <col min="2" max="2" width="150.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="37.21875" customWidth="1"/>
     <col min="4" max="4" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="352.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="352.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -865,7 +967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -873,7 +975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -881,7 +983,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="156" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="156" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -889,7 +991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -897,18 +999,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="202.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -927,33 +1038,33 @@
       </c>
     </row>
     <row r="2" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="10"/>
     </row>
     <row r="4" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="A4" s="10"/>
     </row>
     <row r="5" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
+      <c r="A5" s="10"/>
     </row>
     <row r="6" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+      <c r="A6" s="10"/>
     </row>
     <row r="7" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+      <c r="A7" s="10"/>
     </row>
     <row r="8" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
+      <c r="A8" s="10"/>
     </row>
     <row r="9" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
+      <c r="A9" s="10"/>
     </row>
     <row r="10" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+      <c r="A10" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/log/更新list.xlsx
+++ b/log/更新list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP List Check Tool_v4.3_20250724\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL\MP_List_Check_Tool_v4.4_20250731\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103AF526-83FB-4624-8BC6-0B36AB6D2C37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BBC591-01CB-4C4F-AFB4-DC1E66A8FCD7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="更新日志" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -465,6 +465,16 @@
 a.修正Y轴刻度会出现小数点问题，保持刻度只出现整数；
 b.修正下拉框不是自定义时可编辑的bug.</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP List Check Tool_v4.4_20250731</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新list：
+1.Analyse标签页：
+a.更改更新次数统计（项目统计下“ALL”选项）的等级筛选规则，由原规则：看每个项目第一次更新的字符为主-&gt;改为：选择关键字只算有关键字的部分；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -577,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -608,6 +618,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -939,16 +952,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" customWidth="1"/>
-    <col min="2" max="2" width="150.44140625" customWidth="1"/>
-    <col min="3" max="3" width="37.21875" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.375" customWidth="1"/>
+    <col min="2" max="2" width="150.5" customWidth="1"/>
+    <col min="3" max="3" width="37.25" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,7 +972,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="352.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="352.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -967,7 +980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -975,7 +988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -983,7 +996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="156" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -991,7 +1004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -999,7 +1012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1007,12 +1020,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="202.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="189" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1027,43 +1048,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CFCA9A2-FA7E-4254-B2E7-8F323DED8BBB}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="167.33203125" customWidth="1"/>
+    <col min="1" max="1" width="167.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
     </row>
-    <row r="4" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
     </row>
-    <row r="5" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10"/>
     </row>
-    <row r="7" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
     </row>
-    <row r="8" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
     </row>
-    <row r="9" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10"/>
     </row>
-    <row r="10" spans="1:1" ht="181.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
     </row>
   </sheetData>

--- a/log/更新list.xlsx
+++ b/log/更新list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL\MP_List_Check_Tool_v4.4_20250731\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v4.5_20251020\log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BBC591-01CB-4C4F-AFB4-DC1E66A8FCD7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68DA6D6-6E94-4CF0-92DF-7FBE3597FE25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="更新日志" sheetId="1" r:id="rId1"/>
     <sheet name="TOOL功能总结" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -475,6 +475,40 @@
     <t>更新list：
 1.Analyse标签页：
 a.更改更新次数统计（项目统计下“ALL”选项）的等级筛选规则，由原规则：看每个项目第一次更新的字符为主-&gt;改为：选择关键字只算有关键字的部分；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP List Check Tool_v4.5_20251020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新list：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.Check标签页:
+a.修改序号检查&amp;校正规则；
+b.修改因序号变化其它项检查规则；
+c.新增“项目号位置校正”button，位于分项检查，当有相同项目号的信息未放一起并且序号连续时启用，功能为将后续有相同项目号合并至原项目号下面并且重新排序号；
+2.Analyse标签页：
+a.补充最近新的IC、glass信息，修改因序号变化而引起的Bug。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -613,14 +647,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,7 +986,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.375" customWidth="1"/>
@@ -1032,8 +1066,16 @@
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1059,33 +1101,33 @@
       </c>
     </row>
     <row r="2" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10"/>
+      <c r="A3" s="11"/>
     </row>
     <row r="4" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
+      <c r="A4" s="11"/>
     </row>
     <row r="5" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
+      <c r="A5" s="11"/>
     </row>
     <row r="6" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10"/>
+      <c r="A6" s="11"/>
     </row>
     <row r="7" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10"/>
+      <c r="A7" s="11"/>
     </row>
     <row r="8" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10"/>
+      <c r="A8" s="11"/>
     </row>
     <row r="9" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10"/>
+      <c r="A9" s="11"/>
     </row>
     <row r="10" spans="1:1" ht="181.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
+      <c r="A10" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/log/更新list.xlsx
+++ b/log/更新list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v4.5_20251020\log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL\MP_List_Check_Tool_v4.6_20251226\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68DA6D6-6E94-4CF0-92DF-7FBE3597FE25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3C1A2A-64C9-4CFA-96FD-9923830FDA12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -505,9 +505,40 @@
 1.Check标签页:
 a.修改序号检查&amp;校正规则；
 b.修改因序号变化其它项检查规则；
-c.新增“项目号位置校正”button，位于分项检查，当有相同项目号的信息未放一起并且序号连续时启用，功能为将后续有相同项目号合并至原项目号下面并且重新排序号；
+c.新增“项目号位置校正”button，位于分项检查，当有相同项目号的信息未放一起并且序号未连续时启用，功能为将后续有相同项目号合并至原项目号下面并且重新排列序号，结果将保存到modified_excel_file.xlsx（由于项目信息挪动逻辑为重新排序项目信息，无法复制原excel表的公式，因此modified_excel_file.xlsx最后只保留"MP Project List（internal）"sheet信息）；
 2.Analyse标签页：
 a.补充最近新的IC、glass信息，修改因序号变化而引起的Bug。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP List Check Tool_v4.6_20251226</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新list：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.Analyse标签页：
+a.补充新增IC、glass信息，添加补丁兼容部分表格信息；
+b.修正信息检索分类的bug。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -986,7 +1017,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.375" customWidth="1"/>
@@ -1070,12 +1101,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
